--- a/output/pdf_financials_xlsx/NOW.xlsx
+++ b/output/pdf_financials_xlsx/NOW.xlsx
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.046796</v>
+        <v>-0.046796</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.049717</v>
+        <v>-0.049717</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.046796</v>
+        <v>-0.046796</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.049717</v>
+        <v>-0.049717</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.046796</v>
+        <v>-0.046796</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.049717</v>
+        <v>-0.049717</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>2.3398</v>
+        <v>-2.3398</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2.48585</v>
+        <v>-2.48585</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.046796</v>
+        <v>-0.046796</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.049717</v>
+        <v>-0.049717</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.046796</v>
+        <v>-0.046796</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.049717</v>
+        <v>-0.049717</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -2146,19 +2146,19 @@
         <v>0.214616</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.674815000000001</v>
+        <v>0.340097</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>10.851122</v>
+        <v>0.38443</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>5.558053</v>
+        <v>0.669631</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>11.435612</v>
+        <v>1.012136</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>11.832437</v>
+        <v>0.31983</v>
       </c>
     </row>
     <row r="49">
@@ -3051,19 +3051,19 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>5.40161</v>
+        <v>1.550305</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>8.598311000000001</v>
+        <v>3.955272</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>14.432014</v>
+        <v>3.854844</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>18.905804</v>
+        <v>8.948237000000001</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>13.483081</v>
+        <v>9.291085000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3394,10 +3394,10 @@
         <v>5.391319</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>2.556259</v>
+        <v>0.392548</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>1.673712</v>
+        <v>1.295047</v>
       </c>
     </row>
     <row r="86">
@@ -3583,10 +3583,10 @@
         <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>0.077164</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>-1.423722</v>
       </c>
       <c r="G91" s="3" t="n">
         <v>-4.067831</v>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.030344</v>
+        <v>0.04181</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherCurrentLiabilities</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CurrentLiabilities</t>
+          <t>OtherNonCurrentLiabilities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -9784,7 +9784,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -10192,7 +10196,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -11384,7 +11388,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -12438,7 +12446,11 @@
           <t>Warrant reserve (Note 4 b)</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -17202,10 +17214,10 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>0.046796</v>
+        <v>-0.046796</v>
       </c>
       <c r="H214" s="5" t="n">
-        <v>0.049717</v>
+        <v>-0.049717</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NOW.xlsx
+++ b/output/pdf_financials_xlsx/NOW.xlsx
@@ -1684,19 +1684,19 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>9.102914999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.809012</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.77434</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.577716</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>3.465009</v>
       </c>
     </row>
     <row r="35">
@@ -1750,19 +1750,19 @@
         <v>0</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>9.102914999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.809012</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.77434</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.577716</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>3.465009</v>
       </c>
     </row>
     <row r="37">
@@ -2146,19 +2146,19 @@
         <v>0.214616</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.340097</v>
+        <v>0.5719</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.38443</v>
+        <v>7.04211</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.669631</v>
+        <v>2.783713</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.012136</v>
+        <v>8.857896</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.31983</v>
+        <v>8.367428</v>
       </c>
     </row>
     <row r="49">
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>0</v>
+        <v>0.765037</v>
       </c>
       <c r="F69" s="3" t="n">
         <v>2.127244</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.765037</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>2.127244</v>
@@ -3051,19 +3051,19 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1.550305</v>
+        <v>4.636573</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>3.955272</v>
+        <v>8.598311000000001</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>3.854844</v>
+        <v>14.432014</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>8.948237000000001</v>
+        <v>18.905804</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>9.291085000000001</v>
+        <v>13.483081</v>
       </c>
     </row>
     <row r="76">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>1.418751</v>
+        <v>0.653714</v>
       </c>
       <c r="F77" s="3" t="n">
         <v>11.24842</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>1.418751</v>
+        <v>0.653714</v>
       </c>
       <c r="F79" s="3" t="n">
         <v>11.24842</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>2.141374</v>
+        <v>2.906411</v>
       </c>
       <c r="F85" s="3" t="n">
         <v>4.446729</v>
@@ -3394,10 +3394,10 @@
         <v>5.391319</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.392548</v>
+        <v>2.556259</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>1.295047</v>
+        <v>1.673712</v>
       </c>
     </row>
     <row r="86">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>OtherCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LongTermDebt</t>
+          <t>CurrentDebt</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
